--- a/GWD Data/Gutter&Clamp.xlsx
+++ b/GWD Data/Gutter&Clamp.xlsx
@@ -1,12 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Gutter&amp;Clamp" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -139,28 +143,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
-    <font/>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -168,33 +180,40 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D2E9"/>
-        <bgColor rgb="FFD9D2E9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAD1DC"/>
-        <bgColor rgb="FFEAD1DC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="12">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -203,6 +222,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -211,6 +232,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -239,6 +261,7 @@
       <left style="thin">
         <color rgb="FF3D3D3D"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
@@ -247,6 +270,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
@@ -255,6 +280,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF3D3D3D"/>
       </right>
@@ -275,6 +301,7 @@
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -283,6 +310,7 @@
       <right style="thin">
         <color rgb="FF3D3D3D"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF3D3D3D"/>
       </bottom>
@@ -297,6 +325,7 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -305,201 +334,365 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+  <cellXfs count="36">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -640,24 +833,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFF00FF"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="8.0"/>
-    <col customWidth="1" min="2" max="2" width="30.75"/>
-    <col customWidth="1" min="3" max="5" width="8.0"/>
-    <col customWidth="1" min="6" max="6" width="10.0"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFCF40D4-51D0-4F5D-9D03-DDBB3082B9A6}">
+  <dimension ref="A1:F120"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -667,9 +858,9 @@
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="12.75">
       <c r="A2" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -679,7 +870,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="7"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="12.75">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -699,7 +890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="12.75">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>8</v>
@@ -709,7 +900,7 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="12.75">
       <c r="A5" s="10"/>
       <c r="B5" s="9" t="s">
         <v>9</v>
@@ -719,30 +910,30 @@
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="12.75">
       <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="14">
-        <v>10.5</v>
-      </c>
-      <c r="E6" s="14">
-        <v>475.0</v>
-      </c>
-      <c r="F6" s="15">
+      <c r="D6" s="12">
+        <v>10.50</v>
+      </c>
+      <c r="E6" s="12">
+        <v>475</v>
+      </c>
+      <c r="F6" s="13">
         <f>D6*E6</f>
-        <v>4987.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16"/>
-      <c r="B7" s="12" t="s">
+        <v>4987.50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="12.75">
+      <c r="A7" s="14"/>
+      <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="10"/>
@@ -750,253 +941,253 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
     </row>
-    <row r="8">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18" t="s">
+    <row r="8" spans="1:6" ht="12.75">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="19">
+      <c r="F8" s="17">
         <f>SUM(F6:F7)</f>
-        <v>4987.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18" t="s">
+        <v>4987.50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="12.75">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="19">
+      <c r="F9" s="17">
         <f>F8*0.01</f>
         <v>49.875</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18" t="s">
+    <row r="10" spans="1:6" ht="12.75">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="19">
+      <c r="F10" s="17">
         <f>F8+F9</f>
         <v>5037.375</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18" t="s">
+    <row r="11" spans="1:6" ht="12.75">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="19">
+      <c r="F11" s="17">
         <f>F10*0.15</f>
-        <v>755.60625</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18" t="s">
+        <v>755.60625000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="12.75">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="19">
+      <c r="F12" s="17">
         <f>F10+F11</f>
-        <v>5792.98125</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18" t="s">
+        <v>5792.9812499999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="12.75">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="19">
+      <c r="F13" s="17">
         <f>F12</f>
-        <v>5792.98125</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18" t="s">
+        <v>5792.9812499999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="12.75">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="20">
-        <f>round((F13/10),2)</f>
-        <v>579.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17">
-        <v>116.0</v>
+      <c r="F14" s="18">
+        <f>ROUND((F13/10),2)</f>
+        <v>579.30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="12.75">
+      <c r="A15" s="15">
+        <v>116</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="15">
         <v>0.33</v>
       </c>
-      <c r="E15" s="21">
-        <v>784.0</v>
-      </c>
-      <c r="F15" s="22">
-        <f t="shared" ref="F15:F17" si="1">D15*E15</f>
+      <c r="E15" s="15">
+        <v>784</v>
+      </c>
+      <c r="F15" s="19">
+        <f>D15*E15</f>
         <v>258.72</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17">
-        <v>117.0</v>
+    <row r="16" spans="1:6" ht="12.75">
+      <c r="A16" s="15">
+        <v>117</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="17">
-        <v>0.4</v>
-      </c>
-      <c r="E16" s="21">
-        <v>714.0</v>
-      </c>
-      <c r="F16" s="22">
-        <f t="shared" si="1"/>
-        <v>285.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17">
-        <v>114.0</v>
+      <c r="D16" s="15">
+        <v>0.40</v>
+      </c>
+      <c r="E16" s="15">
+        <v>714</v>
+      </c>
+      <c r="F16" s="19">
+        <f>D16*E16</f>
+        <v>285.60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="12.75">
+      <c r="A17" s="15">
+        <v>114</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="17">
-        <v>0.4</v>
-      </c>
-      <c r="E17" s="21">
-        <v>645.0</v>
-      </c>
-      <c r="F17" s="22">
-        <f t="shared" si="1"/>
+      <c r="D17" s="15">
+        <v>0.40</v>
+      </c>
+      <c r="E17" s="15">
+        <v>645</v>
+      </c>
+      <c r="F17" s="19">
+        <f>D17*E17</f>
         <v>258</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="23"/>
-      <c r="B18" s="18" t="s">
+    <row r="18" spans="1:6" ht="12.75">
+      <c r="A18" s="20"/>
+      <c r="B18" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="19">
+      <c r="F18" s="17">
         <f>SUM(F15:F17)</f>
         <v>802.32</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="23"/>
-      <c r="B19" s="18" t="s">
+    <row r="19" spans="1:6" ht="12.75">
+      <c r="A19" s="20"/>
+      <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="19">
+      <c r="F19" s="17">
         <f>F18*0.01</f>
-        <v>8.0232</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23"/>
-      <c r="B20" s="18" t="s">
+        <v>8.0231999999999992</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="12.75">
+      <c r="A20" s="20"/>
+      <c r="B20" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="19">
+      <c r="F20" s="17">
         <f>SUM(F18:F19)</f>
-        <v>810.3432</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23"/>
-      <c r="B21" s="18" t="s">
+        <v>810.34320000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="12.75">
+      <c r="A21" s="20"/>
+      <c r="B21" s="16" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="19">
+      <c r="F21" s="17">
         <f>F20*0.15</f>
         <v>121.55148</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="23"/>
-      <c r="B22" s="18" t="s">
+    <row r="22" spans="1:6" ht="12.75">
+      <c r="A22" s="20"/>
+      <c r="B22" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="19">
+      <c r="F22" s="17">
         <f>SUM(F20:F21)</f>
-        <v>931.89468</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23"/>
-      <c r="B23" s="18" t="s">
+        <v>931.89467999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="12.75">
+      <c r="A23" s="20"/>
+      <c r="B23" s="16" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="19">
+      <c r="F23" s="17">
         <f>F22</f>
-        <v>931.89468</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23"/>
-      <c r="B24" s="18" t="s">
+        <v>931.89467999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="12.75">
+      <c r="A24" s="20"/>
+      <c r="B24" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="20">
-        <f>round((F23/10),2)</f>
+      <c r="F24" s="18">
+        <f>ROUND((F23/10),2)</f>
         <v>93.19</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="24" t="str">
+    <row r="25" spans="1:6" ht="12.75">
+      <c r="A25" s="21" t="str">
         <f>CONCATENATE("Say ₹ ",F14," + ",F24," x Cost Index")</f>
         <v>Say ₹ 579.3 + 93.19 x Cost Index</v>
       </c>
@@ -1006,11 +1197,11 @@
       <c r="E25" s="6"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26">
-      <c r="A26" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="B26" s="26" t="s">
+    <row r="26" spans="1:6" ht="12.75">
+      <c r="A26" s="22">
+        <v>0</v>
+      </c>
+      <c r="B26" s="23" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="6"/>
@@ -1018,39 +1209,39 @@
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27">
-      <c r="A27" s="25" t="s">
+    <row r="27" spans="1:6" ht="12.75">
+      <c r="A27" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="27"/>
-      <c r="B28" s="28" t="s">
+    <row r="28" spans="1:6" ht="12.75">
+      <c r="A28" s="24"/>
+      <c r="B28" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-    </row>
-    <row r="29">
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+    </row>
+    <row r="29" spans="1:6" ht="12.75">
       <c r="A29" s="10"/>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="10"/>
@@ -1058,30 +1249,30 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
     </row>
-    <row r="30">
-      <c r="A30" s="29" t="s">
+    <row r="30" spans="1:6" ht="12.75">
+      <c r="A30" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="32">
-        <v>10.5</v>
-      </c>
-      <c r="E30" s="32">
-        <v>613.0</v>
-      </c>
-      <c r="F30" s="33">
+      <c r="D30" s="27">
+        <v>10.50</v>
+      </c>
+      <c r="E30" s="27">
+        <v>613</v>
+      </c>
+      <c r="F30" s="28">
         <f>D30*E30</f>
-        <v>6436.5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="16"/>
-      <c r="B31" s="30" t="s">
+        <v>6436.50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="12.75">
+      <c r="A31" s="14"/>
+      <c r="B31" s="25" t="s">
         <v>13</v>
       </c>
       <c r="C31" s="10"/>
@@ -1089,253 +1280,253 @@
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
     </row>
-    <row r="32">
-      <c r="A32" s="34"/>
-      <c r="B32" s="35" t="s">
+    <row r="32" spans="1:6" ht="12.75">
+      <c r="A32" s="29"/>
+      <c r="B32" s="30" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="7"/>
-      <c r="F32" s="36">
+      <c r="F32" s="31">
         <f>SUM(F30:F31)</f>
-        <v>6436.5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="34"/>
-      <c r="B33" s="35" t="s">
+        <v>6436.50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="12.75">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="36">
+      <c r="F33" s="31">
         <f>F32*0.01</f>
         <v>64.365</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="34"/>
-      <c r="B34" s="35" t="s">
+    <row r="34" spans="1:6" ht="12.75">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="36">
+      <c r="F34" s="31">
         <f>F32+F33</f>
-        <v>6500.865</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="34"/>
-      <c r="B35" s="35" t="s">
+        <v>6500.8649999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="12.75">
+      <c r="A35" s="29"/>
+      <c r="B35" s="30" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="7"/>
-      <c r="F35" s="36">
+      <c r="F35" s="31">
         <f>F34*0.15</f>
-        <v>975.12975</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="34"/>
-      <c r="B36" s="35" t="s">
+        <v>975.12974999999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="12.75">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="7"/>
-      <c r="F36" s="36">
+      <c r="F36" s="31">
         <f>F34+F35</f>
-        <v>7475.99475</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="34"/>
-      <c r="B37" s="35" t="s">
+        <v>7475.9947499999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="12.75">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="7"/>
-      <c r="F37" s="36">
+      <c r="F37" s="31">
         <f>F36</f>
-        <v>7475.99475</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="34"/>
-      <c r="B38" s="35" t="s">
+        <v>7475.9947499999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="12.75">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="37">
-        <f>round((F37/10),2)</f>
-        <v>747.6</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="34">
-        <v>116.0</v>
-      </c>
-      <c r="B39" s="28" t="s">
+      <c r="F38" s="32">
+        <f>ROUND((F37/10),2)</f>
+        <v>747.60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="12.75">
+      <c r="A39" s="29">
+        <v>116</v>
+      </c>
+      <c r="B39" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="29">
         <v>0.33</v>
       </c>
-      <c r="E39" s="38">
-        <v>784.0</v>
-      </c>
-      <c r="F39" s="39">
-        <f t="shared" ref="F39:F41" si="2">D39*E39</f>
+      <c r="E39" s="29">
+        <v>784</v>
+      </c>
+      <c r="F39" s="33">
+        <f>D39*E39</f>
         <v>258.72</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="34">
-        <v>117.0</v>
-      </c>
-      <c r="B40" s="28" t="s">
+    <row r="40" spans="1:6" ht="12.75">
+      <c r="A40" s="29">
+        <v>117</v>
+      </c>
+      <c r="B40" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="34">
-        <v>0.4</v>
-      </c>
-      <c r="E40" s="38">
-        <v>714.0</v>
-      </c>
-      <c r="F40" s="39">
-        <f t="shared" si="2"/>
-        <v>285.6</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="34">
-        <v>114.0</v>
-      </c>
-      <c r="B41" s="28" t="s">
+      <c r="D40" s="29">
+        <v>0.40</v>
+      </c>
+      <c r="E40" s="29">
+        <v>714</v>
+      </c>
+      <c r="F40" s="33">
+        <f>D40*E40</f>
+        <v>285.60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="12.75">
+      <c r="A41" s="29">
+        <v>114</v>
+      </c>
+      <c r="B41" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="34">
-        <v>0.4</v>
-      </c>
-      <c r="E41" s="38">
-        <v>645.0</v>
-      </c>
-      <c r="F41" s="39">
-        <f t="shared" si="2"/>
+      <c r="D41" s="29">
+        <v>0.40</v>
+      </c>
+      <c r="E41" s="29">
+        <v>645</v>
+      </c>
+      <c r="F41" s="33">
+        <f>D41*E41</f>
         <v>258</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="40"/>
-      <c r="B42" s="35" t="s">
+    <row r="42" spans="1:6" ht="12.75">
+      <c r="A42" s="34"/>
+      <c r="B42" s="30" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="7"/>
-      <c r="F42" s="36">
+      <c r="F42" s="31">
         <f>SUM(F39:F41)</f>
         <v>802.32</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="40"/>
-      <c r="B43" s="35" t="s">
+    <row r="43" spans="1:6" ht="12.75">
+      <c r="A43" s="34"/>
+      <c r="B43" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="7"/>
-      <c r="F43" s="36">
+      <c r="F43" s="31">
         <f>F42*0.01</f>
-        <v>8.0232</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="40"/>
-      <c r="B44" s="35" t="s">
+        <v>8.0231999999999992</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="12.75">
+      <c r="A44" s="34"/>
+      <c r="B44" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="7"/>
-      <c r="F44" s="36">
+      <c r="F44" s="31">
         <f>SUM(F42:F43)</f>
-        <v>810.3432</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="40"/>
-      <c r="B45" s="35" t="s">
+        <v>810.34320000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="12.75">
+      <c r="A45" s="34"/>
+      <c r="B45" s="30" t="s">
         <v>17</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="7"/>
-      <c r="F45" s="36">
+      <c r="F45" s="31">
         <f>F44*0.15</f>
         <v>121.55148</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="40"/>
-      <c r="B46" s="35" t="s">
+    <row r="46" spans="1:6" ht="12.75">
+      <c r="A46" s="34"/>
+      <c r="B46" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="36">
+      <c r="F46" s="31">
         <f>SUM(F44:F45)</f>
-        <v>931.89468</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="40"/>
-      <c r="B47" s="35" t="s">
+        <v>931.89467999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="12.75">
+      <c r="A47" s="34"/>
+      <c r="B47" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="7"/>
-      <c r="F47" s="36">
+      <c r="F47" s="31">
         <f>F46</f>
-        <v>931.89468</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="40"/>
-      <c r="B48" s="35" t="s">
+        <v>931.89467999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="12.75">
+      <c r="A48" s="34"/>
+      <c r="B48" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="7"/>
-      <c r="F48" s="37">
-        <f>round((F47/10),2)</f>
+      <c r="F48" s="32">
+        <f>ROUND((F47/10),2)</f>
         <v>93.19</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="41" t="str">
+    <row r="49" spans="1:6" ht="12.75">
+      <c r="A49" s="35" t="str">
         <f>CONCATENATE("Say ₹ ",F38," + ",F48," x Cost Index")</f>
         <v>Say ₹ 747.6 + 93.19 x Cost Index</v>
       </c>
@@ -1345,11 +1536,11 @@
       <c r="E49" s="6"/>
       <c r="F49" s="7"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" ht="12.75">
       <c r="A50" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="B50" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="6"/>
@@ -1357,7 +1548,7 @@
       <c r="E50" s="6"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" ht="12.75">
       <c r="A51" s="4" t="s">
         <v>2</v>
       </c>
@@ -1377,7 +1568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6" ht="12.75">
       <c r="A52" s="8"/>
       <c r="B52" s="9" t="s">
         <v>8</v>
@@ -1387,7 +1578,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6" ht="12.75">
       <c r="A53" s="10"/>
       <c r="B53" s="9" t="s">
         <v>9</v>
@@ -1397,30 +1588,30 @@
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
     </row>
-    <row r="54">
-      <c r="A54" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="B54" s="12" t="s">
+    <row r="54" spans="1:6" ht="12.75">
+      <c r="A54" s="12">
+        <v>0</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D54" s="14">
-        <v>10.5</v>
-      </c>
-      <c r="E54" s="14">
-        <v>340.0</v>
-      </c>
-      <c r="F54" s="15">
+      <c r="D54" s="12">
+        <v>10.50</v>
+      </c>
+      <c r="E54" s="12">
+        <v>340</v>
+      </c>
+      <c r="F54" s="13">
         <f>D54*E54</f>
         <v>3570</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6" ht="12.75">
       <c r="A55" s="10"/>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C55" s="10"/>
@@ -1428,253 +1619,253 @@
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
     </row>
-    <row r="56">
-      <c r="A56" s="17"/>
-      <c r="B56" s="18" t="s">
+    <row r="56" spans="1:6" ht="12.75">
+      <c r="A56" s="15"/>
+      <c r="B56" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="7"/>
-      <c r="F56" s="19">
+      <c r="F56" s="17">
         <f>SUM(F54:F55)</f>
         <v>3570</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="17"/>
-      <c r="B57" s="18" t="s">
+    <row r="57" spans="1:6" ht="12.75">
+      <c r="A57" s="15"/>
+      <c r="B57" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="7"/>
-      <c r="F57" s="19">
+      <c r="F57" s="17">
         <f>F56*0.01</f>
-        <v>35.7</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17"/>
-      <c r="B58" s="18" t="s">
+        <v>35.70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="12.75">
+      <c r="A58" s="15"/>
+      <c r="B58" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
-      <c r="F58" s="19">
+      <c r="F58" s="17">
         <f>F56+F57</f>
-        <v>3605.7</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17"/>
-      <c r="B59" s="18" t="s">
+        <v>3605.70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="12.75">
+      <c r="A59" s="15"/>
+      <c r="B59" s="16" t="s">
         <v>17</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="7"/>
-      <c r="F59" s="19">
+      <c r="F59" s="17">
         <f>F58*0.15</f>
         <v>540.855</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="17"/>
-      <c r="B60" s="18" t="s">
+    <row r="60" spans="1:6" ht="12.75">
+      <c r="A60" s="15"/>
+      <c r="B60" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="7"/>
-      <c r="F60" s="19">
+      <c r="F60" s="17">
         <f>F58+F59</f>
-        <v>4146.555</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17"/>
-      <c r="B61" s="18" t="s">
+        <v>4146.5550000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="12.75">
+      <c r="A61" s="15"/>
+      <c r="B61" s="16" t="s">
         <v>18</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="7"/>
-      <c r="F61" s="19">
+      <c r="F61" s="17">
         <f>F60</f>
-        <v>4146.555</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="17"/>
-      <c r="B62" s="18" t="s">
+        <v>4146.5550000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="12.75">
+      <c r="A62" s="15"/>
+      <c r="B62" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="7"/>
-      <c r="F62" s="20">
-        <f>round((F61/10),2)</f>
+      <c r="F62" s="18">
+        <f>ROUND((F61/10),2)</f>
         <v>414.66</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="17">
-        <v>116.0</v>
+    <row r="63" spans="1:6" ht="12.75">
+      <c r="A63" s="15">
+        <v>116</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="17">
+      <c r="D63" s="15">
         <v>0.33</v>
       </c>
-      <c r="E63" s="21">
-        <v>784.0</v>
-      </c>
-      <c r="F63" s="22">
-        <f t="shared" ref="F63:F65" si="3">D63*E63</f>
+      <c r="E63" s="15">
+        <v>784</v>
+      </c>
+      <c r="F63" s="19">
+        <f>D63*E63</f>
         <v>258.72</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="17">
-        <v>117.0</v>
+    <row r="64" spans="1:6" ht="12.75">
+      <c r="A64" s="15">
+        <v>117</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="17">
-        <v>0.4</v>
-      </c>
-      <c r="E64" s="21">
-        <v>714.0</v>
-      </c>
-      <c r="F64" s="22">
-        <f t="shared" si="3"/>
-        <v>285.6</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="17">
-        <v>114.0</v>
+      <c r="D64" s="15">
+        <v>0.40</v>
+      </c>
+      <c r="E64" s="15">
+        <v>714</v>
+      </c>
+      <c r="F64" s="19">
+        <f>D64*E64</f>
+        <v>285.60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="12.75">
+      <c r="A65" s="15">
+        <v>114</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="17">
-        <v>0.4</v>
-      </c>
-      <c r="E65" s="21">
-        <v>645.0</v>
-      </c>
-      <c r="F65" s="22">
-        <f t="shared" si="3"/>
+      <c r="D65" s="15">
+        <v>0.40</v>
+      </c>
+      <c r="E65" s="15">
+        <v>645</v>
+      </c>
+      <c r="F65" s="19">
+        <f>D65*E65</f>
         <v>258</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="23"/>
-      <c r="B66" s="18" t="s">
+    <row r="66" spans="1:6" ht="12.75">
+      <c r="A66" s="20"/>
+      <c r="B66" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="7"/>
-      <c r="F66" s="19">
+      <c r="F66" s="17">
         <f>SUM(F63:F65)</f>
         <v>802.32</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="23"/>
-      <c r="B67" s="18" t="s">
+    <row r="67" spans="1:6" ht="12.75">
+      <c r="A67" s="20"/>
+      <c r="B67" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="7"/>
-      <c r="F67" s="19">
+      <c r="F67" s="17">
         <f>F66*0.01</f>
-        <v>8.0232</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="23"/>
-      <c r="B68" s="18" t="s">
+        <v>8.0231999999999992</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="12.75">
+      <c r="A68" s="20"/>
+      <c r="B68" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="7"/>
-      <c r="F68" s="19">
+      <c r="F68" s="17">
         <f>SUM(F66:F67)</f>
-        <v>810.3432</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="23"/>
-      <c r="B69" s="18" t="s">
+        <v>810.34320000000002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="12.75">
+      <c r="A69" s="20"/>
+      <c r="B69" s="16" t="s">
         <v>17</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="7"/>
-      <c r="F69" s="19">
+      <c r="F69" s="17">
         <f>F68*0.15</f>
         <v>121.55148</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="23"/>
-      <c r="B70" s="18" t="s">
+    <row r="70" spans="1:6" ht="12.75">
+      <c r="A70" s="20"/>
+      <c r="B70" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="7"/>
-      <c r="F70" s="19">
+      <c r="F70" s="17">
         <f>SUM(F68:F69)</f>
-        <v>931.89468</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="23"/>
-      <c r="B71" s="18" t="s">
+        <v>931.89467999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="12.75">
+      <c r="A71" s="20"/>
+      <c r="B71" s="16" t="s">
         <v>18</v>
       </c>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="7"/>
-      <c r="F71" s="19">
+      <c r="F71" s="17">
         <f>F70</f>
-        <v>931.89468</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="23"/>
-      <c r="B72" s="18" t="s">
+        <v>931.89467999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="12.75">
+      <c r="A72" s="20"/>
+      <c r="B72" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="7"/>
-      <c r="F72" s="20">
-        <f>round((F71/10),2)</f>
+      <c r="F72" s="18">
+        <f>ROUND((F71/10),2)</f>
         <v>93.19</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="24" t="str">
+    <row r="73" spans="1:6" ht="12.75">
+      <c r="A73" s="21" t="str">
         <f>CONCATENATE("Say ₹ ",F62," + ",F72," x Cost Index")</f>
         <v>Say ₹ 414.66 + 93.19 x Cost Index</v>
       </c>
@@ -1684,11 +1875,11 @@
       <c r="E73" s="6"/>
       <c r="F73" s="7"/>
     </row>
-    <row r="74">
-      <c r="A74" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="B74" s="43" t="s">
+    <row r="74" spans="1:6" ht="12.75">
+      <c r="A74" s="22">
+        <v>0</v>
+      </c>
+      <c r="B74" s="23" t="s">
         <v>30</v>
       </c>
       <c r="C74" s="6"/>
@@ -1696,39 +1887,39 @@
       <c r="E74" s="6"/>
       <c r="F74" s="7"/>
     </row>
-    <row r="75">
-      <c r="A75" s="25" t="s">
+    <row r="75" spans="1:6" ht="12.75">
+      <c r="A75" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B75" s="25" t="s">
+      <c r="B75" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="25" t="s">
+      <c r="C75" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="25" t="s">
+      <c r="D75" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="25" t="s">
+      <c r="E75" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F75" s="25" t="s">
+      <c r="F75" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="27"/>
-      <c r="B76" s="28" t="s">
+    <row r="76" spans="1:6" ht="12.75">
+      <c r="A76" s="24"/>
+      <c r="B76" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C76" s="27"/>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-    </row>
-    <row r="77">
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" spans="1:6" ht="12.75">
       <c r="A77" s="10"/>
-      <c r="B77" s="28" t="s">
+      <c r="B77" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C77" s="10"/>
@@ -1736,30 +1927,30 @@
       <c r="E77" s="10"/>
       <c r="F77" s="10"/>
     </row>
-    <row r="78">
-      <c r="A78" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="B78" s="30" t="s">
+    <row r="78" spans="1:6" ht="12.75">
+      <c r="A78" s="27">
+        <v>0</v>
+      </c>
+      <c r="B78" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C78" s="31" t="s">
+      <c r="C78" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D78" s="31">
-        <v>11.5</v>
-      </c>
-      <c r="E78" s="32">
-        <v>350.0</v>
-      </c>
-      <c r="F78" s="33">
+      <c r="D78" s="27">
+        <v>11.50</v>
+      </c>
+      <c r="E78" s="27">
+        <v>350</v>
+      </c>
+      <c r="F78" s="28">
         <f>D78*E78</f>
         <v>4025</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:6" ht="12.75">
       <c r="A79" s="10"/>
-      <c r="B79" s="28" t="s">
+      <c r="B79" s="25" t="s">
         <v>32</v>
       </c>
       <c r="C79" s="10"/>
@@ -1767,253 +1958,253 @@
       <c r="E79" s="10"/>
       <c r="F79" s="10"/>
     </row>
-    <row r="80">
-      <c r="A80" s="34"/>
-      <c r="B80" s="35" t="s">
+    <row r="80" spans="1:6" ht="12.75">
+      <c r="A80" s="29"/>
+      <c r="B80" s="30" t="s">
         <v>14</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
       <c r="E80" s="7"/>
-      <c r="F80" s="36">
+      <c r="F80" s="31">
         <f>SUM(F78:F79)</f>
         <v>4025</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="34"/>
-      <c r="B81" s="35" t="s">
+    <row r="81" spans="1:6" ht="12.75">
+      <c r="A81" s="29"/>
+      <c r="B81" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
       <c r="E81" s="7"/>
-      <c r="F81" s="36">
+      <c r="F81" s="31">
         <f>F80*0.01</f>
         <v>40.25</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="34"/>
-      <c r="B82" s="35" t="s">
+    <row r="82" spans="1:6" ht="12.75">
+      <c r="A82" s="29"/>
+      <c r="B82" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
       <c r="E82" s="7"/>
-      <c r="F82" s="36">
+      <c r="F82" s="31">
         <f>F80+F81</f>
         <v>4065.25</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="34"/>
-      <c r="B83" s="35" t="s">
+    <row r="83" spans="1:6" ht="12.75">
+      <c r="A83" s="29"/>
+      <c r="B83" s="30" t="s">
         <v>17</v>
       </c>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="7"/>
-      <c r="F83" s="36">
+      <c r="F83" s="31">
         <f>F82*0.15</f>
         <v>609.7875</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="34"/>
-      <c r="B84" s="35" t="s">
+    <row r="84" spans="1:6" ht="12.75">
+      <c r="A84" s="29"/>
+      <c r="B84" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
       <c r="E84" s="7"/>
-      <c r="F84" s="36">
+      <c r="F84" s="31">
         <f>F82+F83</f>
-        <v>4675.0375</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="34"/>
-      <c r="B85" s="35" t="s">
+        <v>4675.0375000000004</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="12.75">
+      <c r="A85" s="29"/>
+      <c r="B85" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
       <c r="E85" s="7"/>
-      <c r="F85" s="36">
+      <c r="F85" s="31">
         <f>F84</f>
-        <v>4675.0375</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="34"/>
-      <c r="B86" s="35" t="s">
+        <v>4675.0375000000004</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="12.75">
+      <c r="A86" s="29"/>
+      <c r="B86" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="7"/>
-      <c r="F86" s="37">
-        <f>round((F85/10),2)</f>
-        <v>467.5</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="34">
-        <v>116.0</v>
-      </c>
-      <c r="B87" s="28" t="s">
+      <c r="F86" s="32">
+        <f>ROUND((F85/10),2)</f>
+        <v>467.50</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="12.75">
+      <c r="A87" s="29">
+        <v>116</v>
+      </c>
+      <c r="B87" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C87" s="34" t="s">
+      <c r="C87" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D87" s="34">
+      <c r="D87" s="29">
         <v>0.33</v>
       </c>
-      <c r="E87" s="38">
-        <v>784.0</v>
-      </c>
-      <c r="F87" s="39">
-        <f t="shared" ref="F87:F89" si="4">D87*E87</f>
+      <c r="E87" s="29">
+        <v>784</v>
+      </c>
+      <c r="F87" s="33">
+        <f>D87*E87</f>
         <v>258.72</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="34">
-        <v>117.0</v>
-      </c>
-      <c r="B88" s="28" t="s">
+    <row r="88" spans="1:6" ht="12.75">
+      <c r="A88" s="29">
+        <v>117</v>
+      </c>
+      <c r="B88" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C88" s="34" t="s">
+      <c r="C88" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D88" s="34">
-        <v>0.4</v>
-      </c>
-      <c r="E88" s="38">
-        <v>714.0</v>
-      </c>
-      <c r="F88" s="39">
-        <f t="shared" si="4"/>
-        <v>285.6</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="34">
-        <v>114.0</v>
-      </c>
-      <c r="B89" s="28" t="s">
+      <c r="D88" s="29">
+        <v>0.40</v>
+      </c>
+      <c r="E88" s="29">
+        <v>714</v>
+      </c>
+      <c r="F88" s="33">
+        <f>D88*E88</f>
+        <v>285.60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="12.75">
+      <c r="A89" s="29">
+        <v>114</v>
+      </c>
+      <c r="B89" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C89" s="34" t="s">
+      <c r="C89" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D89" s="34">
-        <v>0.4</v>
-      </c>
-      <c r="E89" s="38">
-        <v>645.0</v>
-      </c>
-      <c r="F89" s="39">
-        <f t="shared" si="4"/>
+      <c r="D89" s="29">
+        <v>0.40</v>
+      </c>
+      <c r="E89" s="29">
+        <v>645</v>
+      </c>
+      <c r="F89" s="33">
+        <f>D89*E89</f>
         <v>258</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="40"/>
-      <c r="B90" s="35" t="s">
+    <row r="90" spans="1:6" ht="12.75">
+      <c r="A90" s="34"/>
+      <c r="B90" s="30" t="s">
         <v>24</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="7"/>
-      <c r="F90" s="36">
+      <c r="F90" s="31">
         <f>SUM(F87:F89)</f>
         <v>802.32</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="40"/>
-      <c r="B91" s="35" t="s">
+    <row r="91" spans="1:6" ht="12.75">
+      <c r="A91" s="34"/>
+      <c r="B91" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
       <c r="E91" s="7"/>
-      <c r="F91" s="36">
+      <c r="F91" s="31">
         <f>F90*0.01</f>
-        <v>8.0232</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="40"/>
-      <c r="B92" s="35" t="s">
+        <v>8.0231999999999992</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="12.75">
+      <c r="A92" s="34"/>
+      <c r="B92" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
       <c r="E92" s="7"/>
-      <c r="F92" s="36">
+      <c r="F92" s="31">
         <f>SUM(F90:F91)</f>
-        <v>810.3432</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="40"/>
-      <c r="B93" s="35" t="s">
+        <v>810.34320000000002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="12.75">
+      <c r="A93" s="34"/>
+      <c r="B93" s="30" t="s">
         <v>17</v>
       </c>
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
       <c r="E93" s="7"/>
-      <c r="F93" s="36">
+      <c r="F93" s="31">
         <f>F92*0.15</f>
         <v>121.55148</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="40"/>
-      <c r="B94" s="35" t="s">
+    <row r="94" spans="1:6" ht="12.75">
+      <c r="A94" s="34"/>
+      <c r="B94" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
       <c r="E94" s="7"/>
-      <c r="F94" s="36">
+      <c r="F94" s="31">
         <f>SUM(F92:F93)</f>
-        <v>931.89468</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="40"/>
-      <c r="B95" s="35" t="s">
+        <v>931.89467999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="12.75">
+      <c r="A95" s="34"/>
+      <c r="B95" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
       <c r="E95" s="7"/>
-      <c r="F95" s="36">
+      <c r="F95" s="31">
         <f>F94</f>
-        <v>931.89468</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="40"/>
-      <c r="B96" s="35" t="s">
+        <v>931.89467999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="12.75">
+      <c r="A96" s="34"/>
+      <c r="B96" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
       <c r="E96" s="7"/>
-      <c r="F96" s="37">
-        <f>round((F95/10),2)</f>
+      <c r="F96" s="32">
+        <f>ROUND((F95/10),2)</f>
         <v>93.19</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="41" t="str">
+    <row r="97" spans="1:6" ht="12.75">
+      <c r="A97" s="35" t="str">
         <f>CONCATENATE("Say ₹ ",F86," + ",F96," x Cost Index")</f>
         <v>Say ₹ 467.5 + 93.19 x Cost Index</v>
       </c>
@@ -2023,11 +2214,11 @@
       <c r="E97" s="6"/>
       <c r="F97" s="7"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:6" ht="12.75">
       <c r="A98" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="B98" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B98" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C98" s="6"/>
@@ -2035,7 +2226,7 @@
       <c r="E98" s="6"/>
       <c r="F98" s="7"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:6" ht="12.75">
       <c r="A99" s="4" t="s">
         <v>2</v>
       </c>
@@ -2055,7 +2246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:6" ht="12.75">
       <c r="A100" s="8"/>
       <c r="B100" s="9" t="s">
         <v>34</v>
@@ -2065,7 +2256,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:6" ht="12.75">
       <c r="A101" s="10"/>
       <c r="B101" s="9" t="s">
         <v>9</v>
@@ -2075,274 +2266,274 @@
       <c r="E101" s="10"/>
       <c r="F101" s="10"/>
     </row>
-    <row r="102">
-      <c r="A102" s="21" t="s">
+    <row r="102" spans="1:6" ht="12.75">
+      <c r="A102" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C102" s="17" t="s">
+      <c r="C102" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D102" s="17">
-        <v>10.0</v>
-      </c>
-      <c r="E102" s="21">
-        <v>35.0</v>
-      </c>
-      <c r="F102" s="22">
+      <c r="D102" s="15">
+        <v>10</v>
+      </c>
+      <c r="E102" s="15">
+        <v>35</v>
+      </c>
+      <c r="F102" s="19">
         <f>D102*E102</f>
         <v>350</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="17"/>
-      <c r="B103" s="18" t="s">
+    <row r="103" spans="1:6" ht="12.75">
+      <c r="A103" s="15"/>
+      <c r="B103" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="7"/>
-      <c r="F103" s="19">
+      <c r="F103" s="17">
         <f>SUM(F102)</f>
         <v>350</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="17"/>
-      <c r="B104" s="18" t="s">
+    <row r="104" spans="1:6" ht="12.75">
+      <c r="A104" s="15"/>
+      <c r="B104" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
       <c r="E104" s="7"/>
-      <c r="F104" s="19">
+      <c r="F104" s="17">
         <f>F103*0.01</f>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="17"/>
-      <c r="B105" s="18" t="s">
+        <v>3.50</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="12.75">
+      <c r="A105" s="15"/>
+      <c r="B105" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
       <c r="E105" s="7"/>
-      <c r="F105" s="19">
+      <c r="F105" s="17">
         <f>F103+F104</f>
-        <v>353.5</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="17"/>
-      <c r="B106" s="18" t="s">
+        <v>353.50</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="12.75">
+      <c r="A106" s="15"/>
+      <c r="B106" s="16" t="s">
         <v>17</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="7"/>
-      <c r="F106" s="19">
+      <c r="F106" s="17">
         <f>F105*0.15</f>
         <v>53.025</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="17"/>
-      <c r="B107" s="18" t="s">
+    <row r="107" spans="1:6" ht="12.75">
+      <c r="A107" s="15"/>
+      <c r="B107" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="7"/>
-      <c r="F107" s="19">
+      <c r="F107" s="17">
         <f>F105+F106</f>
         <v>406.525</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="17"/>
-      <c r="B108" s="44" t="s">
+    <row r="108" spans="1:6" ht="12.75">
+      <c r="A108" s="15"/>
+      <c r="B108" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
       <c r="E108" s="7"/>
-      <c r="F108" s="19">
+      <c r="F108" s="17">
         <f>F107</f>
         <v>406.525</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="17"/>
-      <c r="B109" s="44" t="s">
+    <row r="109" spans="1:6" ht="12.75">
+      <c r="A109" s="15"/>
+      <c r="B109" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C109" s="6"/>
       <c r="D109" s="6"/>
       <c r="E109" s="7"/>
-      <c r="F109" s="20">
-        <f>round((F108/10),2)</f>
+      <c r="F109" s="18">
+        <f>ROUND((F108/10),2)</f>
         <v>40.65</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="17">
-        <v>116.0</v>
+    <row r="110" spans="1:6" ht="12.75">
+      <c r="A110" s="15">
+        <v>116</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C110" s="17" t="s">
+      <c r="C110" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D110" s="17">
+      <c r="D110" s="15">
         <v>0.15</v>
       </c>
-      <c r="E110" s="21">
-        <v>784.0</v>
-      </c>
-      <c r="F110" s="22">
-        <f t="shared" ref="F110:F112" si="5">D110*E110</f>
-        <v>117.6</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="17">
-        <v>103.0</v>
+      <c r="E110" s="15">
+        <v>784</v>
+      </c>
+      <c r="F110" s="19">
+        <f>D110*E110</f>
+        <v>117.60</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="12.75">
+      <c r="A111" s="15">
+        <v>103</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C111" s="17" t="s">
+      <c r="C111" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D111" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="E111" s="21">
-        <v>714.0</v>
-      </c>
-      <c r="F111" s="22">
-        <f t="shared" si="5"/>
-        <v>71.4</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="17">
-        <v>114.0</v>
+      <c r="D111" s="15">
+        <v>0.10</v>
+      </c>
+      <c r="E111" s="15">
+        <v>714</v>
+      </c>
+      <c r="F111" s="19">
+        <f>D111*E111</f>
+        <v>71.40</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="12.75">
+      <c r="A112" s="15">
+        <v>114</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C112" s="17" t="s">
+      <c r="C112" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D112" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="E112" s="21">
-        <v>645.0</v>
-      </c>
-      <c r="F112" s="22">
-        <f t="shared" si="5"/>
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="23"/>
-      <c r="B113" s="18" t="s">
+      <c r="D112" s="15">
+        <v>0.10</v>
+      </c>
+      <c r="E112" s="15">
+        <v>645</v>
+      </c>
+      <c r="F112" s="19">
+        <f>D112*E112</f>
+        <v>64.50</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="12.75">
+      <c r="A113" s="20"/>
+      <c r="B113" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
       <c r="E113" s="7"/>
-      <c r="F113" s="19">
+      <c r="F113" s="17">
         <f>SUM(F110:F112)</f>
-        <v>253.5</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="23"/>
-      <c r="B114" s="18" t="s">
+        <v>253.50</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="12.75">
+      <c r="A114" s="20"/>
+      <c r="B114" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
       <c r="E114" s="7"/>
-      <c r="F114" s="19">
+      <c r="F114" s="17">
         <f>F113*0.01</f>
         <v>2.535</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="23"/>
-      <c r="B115" s="18" t="s">
+    <row r="115" spans="1:6" ht="12.75">
+      <c r="A115" s="20"/>
+      <c r="B115" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C115" s="6"/>
       <c r="D115" s="6"/>
       <c r="E115" s="7"/>
-      <c r="F115" s="19">
+      <c r="F115" s="17">
         <f>SUM(F113:F114)</f>
         <v>256.035</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="23"/>
-      <c r="B116" s="18" t="s">
+    <row r="116" spans="1:6" ht="12.75">
+      <c r="A116" s="20"/>
+      <c r="B116" s="16" t="s">
         <v>17</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="6"/>
       <c r="E116" s="7"/>
-      <c r="F116" s="19">
+      <c r="F116" s="17">
         <f>F115*0.15</f>
-        <v>38.40525</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="23"/>
-      <c r="B117" s="18" t="s">
+        <v>38.405250000000002</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="12.75">
+      <c r="A117" s="20"/>
+      <c r="B117" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C117" s="6"/>
       <c r="D117" s="6"/>
       <c r="E117" s="7"/>
-      <c r="F117" s="19">
+      <c r="F117" s="17">
         <f>SUM(F115:F116)</f>
-        <v>294.44025</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="23"/>
-      <c r="B118" s="44" t="s">
+        <v>294.44024999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="12.75">
+      <c r="A118" s="20"/>
+      <c r="B118" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="6"/>
       <c r="E118" s="7"/>
-      <c r="F118" s="19">
+      <c r="F118" s="17">
         <f>F117</f>
-        <v>294.44025</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="23"/>
-      <c r="B119" s="44" t="s">
+        <v>294.44024999999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="12.75">
+      <c r="A119" s="20"/>
+      <c r="B119" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C119" s="6"/>
       <c r="D119" s="6"/>
       <c r="E119" s="7"/>
-      <c r="F119" s="20">
-        <f>round((F118/10),2)</f>
+      <c r="F119" s="18">
+        <f>ROUND((F118/10),2)</f>
         <v>29.44</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="24" t="str">
+    <row r="120" spans="1:6" ht="12.75">
+      <c r="A120" s="21" t="str">
         <f>CONCATENATE("Say ₹ ",F109," + ",F119," x Cost Index")</f>
         <v>Say ₹ 40.65 + 29.44 x Cost Index</v>
       </c>
@@ -2481,9 +2672,6 @@
     <mergeCell ref="B119:E119"/>
     <mergeCell ref="A120:F120"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GWD Data/Gutter&Clamp.xlsx
+++ b/GWD Data/Gutter&Clamp.xlsx
@@ -844,7 +844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFCF40D4-51D0-4F5D-9D03-DDBB3082B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699C605C-C731-4301-A2CF-171D3356B9A6}">
   <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/Gutter&Clamp.xlsx
+++ b/GWD Data/Gutter&Clamp.xlsx
@@ -844,7 +844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699C605C-C731-4301-A2CF-171D3356B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB0DB1-B337-4491-81CA-5BE277E0B9A6}">
   <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
